--- a/US/US_Contenido_t_1.xlsx
+++ b/US/US_Contenido_t_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12892" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12892" uniqueCount="593">
   <si>
     <t>.</t>
   </si>
@@ -1514,6 +1514,9 @@
   </si>
   <si>
     <t>La Colonia # 1</t>
+  </si>
+  <si>
+    <t>1.9</t>
   </si>
   <si>
     <t>Pronto</t>
@@ -5142,7 +5145,7 @@
         <v>429</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -5936,13 +5939,13 @@
     </row>
     <row r="4" spans="1:427">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>431</v>
@@ -6362,7 +6365,7 @@
         <v>431</v>
       </c>
       <c r="EM4" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN4" s="1" t="s">
         <v>431</v>
@@ -7219,13 +7222,13 @@
     </row>
     <row r="5" spans="1:427">
       <c r="A5" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -7367,7 +7370,7 @@
       <c r="EK5" s="1"/>
       <c r="EL5" s="1"/>
       <c r="EM5" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN5" s="1"/>
       <c r="EO5" s="1"/>
@@ -7656,13 +7659,13 @@
     </row>
     <row r="6" spans="1:427">
       <c r="A6" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
@@ -7756,7 +7759,7 @@
         <v>431</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ6" s="1" t="s">
         <v>431</v>
@@ -7939,13 +7942,13 @@
         <v>431</v>
       </c>
       <c r="CR6" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS6" s="1" t="s">
         <v>431</v>
       </c>
       <c r="CT6" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU6" s="1" t="s">
         <v>431</v>
@@ -8104,7 +8107,7 @@
         <v>431</v>
       </c>
       <c r="EU6" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV6" s="1" t="s">
         <v>431</v>
@@ -8170,7 +8173,7 @@
         <v>431</v>
       </c>
       <c r="FQ6" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR6" s="1" t="s">
         <v>431</v>
@@ -8935,13 +8938,13 @@
     </row>
     <row r="7" spans="1:427">
       <c r="A7" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
@@ -8979,7 +8982,7 @@
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -9050,11 +9053,11 @@
       <c r="CP7" s="1"/>
       <c r="CQ7" s="1"/>
       <c r="CR7" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS7" s="1"/>
       <c r="CT7" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU7" s="1"/>
       <c r="CV7" s="1"/>
@@ -9115,7 +9118,7 @@
       <c r="ES7" s="1"/>
       <c r="ET7" s="1"/>
       <c r="EU7" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV7" s="1"/>
       <c r="EW7" s="1"/>
@@ -9139,7 +9142,7 @@
       <c r="FO7" s="1"/>
       <c r="FP7" s="1"/>
       <c r="FQ7" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR7" s="1"/>
       <c r="FS7" s="1"/>
@@ -9400,13 +9403,13 @@
     </row>
     <row r="8" spans="1:427">
       <c r="A8" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>431</v>
@@ -10683,13 +10686,13 @@
     </row>
     <row r="9" spans="1:427">
       <c r="A9" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -11120,13 +11123,13 @@
     </row>
     <row r="10" spans="1:427">
       <c r="A10" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>431</v>
@@ -12403,13 +12406,13 @@
     </row>
     <row r="11" spans="1:427">
       <c r="A11" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -12874,13 +12877,13 @@
     </row>
     <row r="12" spans="1:427">
       <c r="A12" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>431</v>
@@ -14157,13 +14160,13 @@
     </row>
     <row r="13" spans="1:427">
       <c r="A13" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -14594,13 +14597,13 @@
     </row>
     <row r="14" spans="1:427">
       <c r="A14" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>431</v>
@@ -15877,13 +15880,13 @@
     </row>
     <row r="15" spans="1:427">
       <c r="A15" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -16328,13 +16331,13 @@
     </row>
     <row r="16" spans="1:427">
       <c r="A16" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>431</v>
@@ -17611,13 +17614,13 @@
     </row>
     <row r="17" spans="1:427">
       <c r="A17" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -18054,13 +18057,13 @@
     </row>
     <row r="18" spans="1:427">
       <c r="A18" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>431</v>
@@ -19337,13 +19340,13 @@
     </row>
     <row r="19" spans="1:427">
       <c r="A19" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -19778,13 +19781,13 @@
     </row>
     <row r="20" spans="1:427">
       <c r="A20" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>431</v>
@@ -21061,13 +21064,13 @@
     </row>
     <row r="21" spans="1:427">
       <c r="A21" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -21512,13 +21515,13 @@
     </row>
     <row r="22" spans="1:427">
       <c r="A22" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>431</v>
@@ -22523,7 +22526,7 @@
         <v>431</v>
       </c>
       <c r="LZ22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA22" s="1" t="s">
         <v>431</v>
@@ -22795,13 +22798,13 @@
     </row>
     <row r="23" spans="1:427">
       <c r="A23" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -23138,7 +23141,7 @@
       <c r="LX23" s="1"/>
       <c r="LY23" s="1"/>
       <c r="LZ23" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA23" s="1"/>
       <c r="MB23" s="1"/>
@@ -23232,13 +23235,13 @@
     </row>
     <row r="24" spans="1:427">
       <c r="A24" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>431</v>
@@ -24303,7 +24306,7 @@
         <v>440</v>
       </c>
       <c r="MT24" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU24" s="1" t="s">
         <v>440</v>
@@ -24315,10 +24318,10 @@
         <v>438</v>
       </c>
       <c r="MX24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY24" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ24" s="1" t="s">
         <v>452</v>
@@ -24336,10 +24339,10 @@
         <v>440</v>
       </c>
       <c r="NE24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG24" s="1" t="s">
         <v>490</v>
@@ -24372,7 +24375,7 @@
         <v>440</v>
       </c>
       <c r="NQ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR24" s="1" t="s">
         <v>440</v>
@@ -24390,16 +24393,16 @@
         <v>440</v>
       </c>
       <c r="NW24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY24" s="1" t="s">
         <v>440</v>
       </c>
       <c r="NZ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA24" s="1" t="s">
         <v>440</v>
@@ -24408,10 +24411,10 @@
         <v>440</v>
       </c>
       <c r="OC24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE24" s="1" t="s">
         <v>467</v>
@@ -24423,7 +24426,7 @@
         <v>440</v>
       </c>
       <c r="OH24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI24" s="1" t="s">
         <v>443</v>
@@ -24441,10 +24444,10 @@
         <v>480</v>
       </c>
       <c r="ON24" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP24" s="1" t="s">
         <v>438</v>
@@ -24515,13 +24518,13 @@
     </row>
     <row r="25" spans="1:427">
       <c r="A25" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -24882,7 +24885,7 @@
         <v>440</v>
       </c>
       <c r="MT25" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU25" s="1" t="s">
         <v>440</v>
@@ -24894,10 +24897,10 @@
         <v>438</v>
       </c>
       <c r="MX25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY25" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ25" s="1" t="s">
         <v>452</v>
@@ -24915,10 +24918,10 @@
         <v>440</v>
       </c>
       <c r="NE25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG25" s="1" t="s">
         <v>490</v>
@@ -24951,7 +24954,7 @@
         <v>440</v>
       </c>
       <c r="NQ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR25" s="1" t="s">
         <v>440</v>
@@ -24969,16 +24972,16 @@
         <v>440</v>
       </c>
       <c r="NW25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY25" s="1" t="s">
         <v>440</v>
       </c>
       <c r="NZ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA25" s="1" t="s">
         <v>440</v>
@@ -24987,10 +24990,10 @@
         <v>440</v>
       </c>
       <c r="OC25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE25" s="1" t="s">
         <v>467</v>
@@ -25002,7 +25005,7 @@
         <v>440</v>
       </c>
       <c r="OH25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI25" s="1" t="s">
         <v>443</v>
@@ -25020,10 +25023,10 @@
         <v>480</v>
       </c>
       <c r="ON25" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP25" s="1" t="s">
         <v>438</v>
@@ -25054,13 +25057,13 @@
     </row>
     <row r="26" spans="1:427">
       <c r="A26" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>431</v>
@@ -26337,13 +26340,13 @@
     </row>
     <row r="27" spans="1:427">
       <c r="A27" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -26778,13 +26781,13 @@
     </row>
     <row r="28" spans="1:427">
       <c r="A28" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>431</v>
@@ -28061,13 +28064,13 @@
     </row>
     <row r="29" spans="1:427">
       <c r="A29" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -28518,13 +28521,13 @@
     </row>
     <row r="30" spans="1:427">
       <c r="A30" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>431</v>
@@ -29801,13 +29804,13 @@
     </row>
     <row r="31" spans="1:427">
       <c r="A31" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -30242,13 +30245,13 @@
     </row>
     <row r="32" spans="1:427">
       <c r="A32" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>431</v>
@@ -31525,13 +31528,13 @@
     </row>
     <row r="33" spans="1:427">
       <c r="A33" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -31962,13 +31965,13 @@
     </row>
     <row r="34" spans="1:427">
       <c r="A34" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>431</v>
@@ -33245,13 +33248,13 @@
     </row>
     <row r="35" spans="1:427">
       <c r="A35" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -33684,13 +33687,13 @@
     </row>
     <row r="36" spans="1:427">
       <c r="A36" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>431</v>
@@ -34967,13 +34970,13 @@
     </row>
     <row r="37" spans="1:427">
       <c r="A37" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -35406,13 +35409,13 @@
     </row>
     <row r="38" spans="1:427">
       <c r="A38" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>431</v>
@@ -36689,13 +36692,13 @@
     </row>
     <row r="39" spans="1:427">
       <c r="A39" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -37200,13 +37203,13 @@
     </row>
     <row r="40" spans="1:427">
       <c r="A40" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>431</v>
@@ -38483,13 +38486,13 @@
     </row>
     <row r="41" spans="1:427">
       <c r="A41" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -39012,13 +39015,13 @@
     </row>
     <row r="42" spans="1:427">
       <c r="A42" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>431</v>
@@ -40295,13 +40298,13 @@
     </row>
     <row r="43" spans="1:427">
       <c r="A43" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -40744,13 +40747,13 @@
     </row>
     <row r="44" spans="1:427">
       <c r="A44" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>431</v>
@@ -42027,13 +42030,13 @@
     </row>
     <row r="45" spans="1:427">
       <c r="A45" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -42464,13 +42467,13 @@
     </row>
     <row r="46" spans="1:427">
       <c r="A46" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>431</v>
@@ -43747,13 +43750,13 @@
     </row>
     <row r="47" spans="1:427">
       <c r="A47" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -44188,13 +44191,13 @@
     </row>
     <row r="48" spans="1:427">
       <c r="A48" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>431</v>
@@ -45471,13 +45474,13 @@
     </row>
     <row r="49" spans="1:427">
       <c r="A49" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -45908,13 +45911,13 @@
     </row>
     <row r="50" spans="1:427">
       <c r="A50" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>431</v>
@@ -47191,13 +47194,13 @@
     </row>
     <row r="51" spans="1:427">
       <c r="A51" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -47628,13 +47631,13 @@
     </row>
     <row r="52" spans="1:427">
       <c r="A52" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>431</v>
@@ -48911,13 +48914,13 @@
     </row>
     <row r="53" spans="1:427">
       <c r="A53" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -49356,13 +49359,13 @@
     </row>
     <row r="54" spans="1:427">
       <c r="A54" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>431</v>
@@ -50639,13 +50642,13 @@
     </row>
     <row r="55" spans="1:427">
       <c r="A55" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -51076,13 +51079,13 @@
     </row>
     <row r="56" spans="1:427">
       <c r="A56" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>431</v>
@@ -52359,13 +52362,13 @@
     </row>
     <row r="57" spans="1:427">
       <c r="A57" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
